--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3130,119 +3130,6 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>111577743</v>
-      </c>
-      <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Tivsjöflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>562802.8660743404</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6954388.771485241</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3130,6 +3130,2465 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129985367</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562633</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6954441</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129981126</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562686</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6954603</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129981204</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562645</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6954638</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129986595</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>562713</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6954614</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129982476</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>562483</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6954658</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129987474</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>562901</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6954477</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129987449</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>562883</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6954461</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129981132</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91900</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562696</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6954608</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129981136</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>562682</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6954614</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129984723</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>562591</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6954478</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129985177</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>562593</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6954431</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran.  Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129985202</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562577</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6954432</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129982693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562458</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6954577</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129981053</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91900</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562682</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6954614</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129986785</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>562725</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6954475</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129982927</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562571</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6954552</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129981038</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80189</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>562680</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6954592</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129982656</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>562447</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6954609</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129983882</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>562540</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6954488</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129986495</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>562543</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6954644</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129986973</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>562784</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6954384</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129981055</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>562686</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6954603</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129987434</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>562873</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6954448</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129985572</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>562648</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6954498</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3135,7 +3135,7 @@
         <v>129985367</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129981126</v>
       </c>
       <c r="B24" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>129981204</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>129986595</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>129982476</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129987474</v>
+        <v>129981132</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>91903</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,39 +3658,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562901</v>
+        <v>562696</v>
       </c>
       <c r="R28" t="n">
-        <v>6954477</v>
+        <v>6954608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3723,11 +3718,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3757,7 +3747,7 @@
         <v>129987449</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3851,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129981132</v>
+        <v>129981136</v>
       </c>
       <c r="B30" t="n">
-        <v>91900</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,34 +3852,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562696</v>
+        <v>562682</v>
       </c>
       <c r="R30" t="n">
-        <v>6954608</v>
+        <v>6954614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3922,6 +3917,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129981136</v>
+        <v>129987474</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562682</v>
+        <v>562901</v>
       </c>
       <c r="R31" t="n">
-        <v>6954614</v>
+        <v>6954477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4058,7 +4058,7 @@
         <v>129984723</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129985177</v>
+        <v>129985202</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4173,39 +4173,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562593</v>
+        <v>562577</v>
       </c>
       <c r="R33" t="n">
-        <v>6954431</v>
+        <v>6954432</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4238,11 +4229,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran.  Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129985202</v>
+        <v>129985177</v>
       </c>
       <c r="B34" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,30 +4266,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562577</v>
+        <v>562593</v>
       </c>
       <c r="R34" t="n">
-        <v>6954432</v>
+        <v>6954431</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4336,6 +4331,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran.  Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,10 +4362,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129982693</v>
+        <v>129981053</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>91903</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4373,21 +4373,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562458</v>
+        <v>562682</v>
       </c>
       <c r="R35" t="n">
-        <v>6954577</v>
+        <v>6954614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129981053</v>
+        <v>129982693</v>
       </c>
       <c r="B36" t="n">
-        <v>91900</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,21 +4470,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562682</v>
+        <v>562458</v>
       </c>
       <c r="R36" t="n">
-        <v>6954614</v>
+        <v>6954577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
         <v>129986785</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129982927</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>129981038</v>
       </c>
       <c r="B39" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129982656</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>129983882</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129986495</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129986973</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>129981055</v>
       </c>
       <c r="B44" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129987434</v>
+        <v>129985572</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>91625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5403,43 +5403,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562873</v>
+        <v>562648</v>
       </c>
       <c r="R45" t="n">
-        <v>6954448</v>
+        <v>6954498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5498,10 +5485,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129985572</v>
+        <v>129987434</v>
       </c>
       <c r="B46" t="n">
-        <v>91622</v>
+        <v>57898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5509,30 +5496,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562648</v>
+        <v>562873</v>
       </c>
       <c r="R46" t="n">
-        <v>6954498</v>
+        <v>6954448</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129985177</v>
+        <v>129981053</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>91903</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,39 +4266,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562593</v>
+        <v>562682</v>
       </c>
       <c r="R34" t="n">
-        <v>6954431</v>
+        <v>6954614</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4331,11 +4326,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran.  Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4362,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129981053</v>
+        <v>129982693</v>
       </c>
       <c r="B35" t="n">
-        <v>91903</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4373,21 +4363,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4397,10 +4387,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562682</v>
+        <v>562458</v>
       </c>
       <c r="R35" t="n">
-        <v>6954614</v>
+        <v>6954577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,10 +4449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129982693</v>
+        <v>129986785</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,34 +4460,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562458</v>
+        <v>562725</v>
       </c>
       <c r="R36" t="n">
-        <v>6954577</v>
+        <v>6954475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4530,6 +4525,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,7 +4556,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129986785</v>
+        <v>129982927</v>
       </c>
       <c r="B37" t="n">
         <v>57740</v>
@@ -4587,7 +4587,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562725</v>
+        <v>562571</v>
       </c>
       <c r="R37" t="n">
-        <v>6954475</v>
+        <v>6954552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129982927</v>
+        <v>129981038</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>80192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4674,39 +4674,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562571</v>
+        <v>562680</v>
       </c>
       <c r="R38" t="n">
-        <v>6954552</v>
+        <v>6954592</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4739,11 +4734,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4760,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129981038</v>
+        <v>129982656</v>
       </c>
       <c r="B39" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4781,34 +4771,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562680</v>
+        <v>562447</v>
       </c>
       <c r="R39" t="n">
-        <v>6954592</v>
+        <v>6954609</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4841,6 +4836,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4867,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129982656</v>
+        <v>129983882</v>
       </c>
       <c r="B40" t="n">
         <v>57740</v>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562447</v>
+        <v>562540</v>
       </c>
       <c r="R40" t="n">
-        <v>6954609</v>
+        <v>6954488</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129983882</v>
+        <v>129986495</v>
       </c>
       <c r="B41" t="n">
         <v>57740</v>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562540</v>
+        <v>562543</v>
       </c>
       <c r="R41" t="n">
-        <v>6954488</v>
+        <v>6954644</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5081,7 +5081,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129986495</v>
+        <v>129986973</v>
       </c>
       <c r="B42" t="n">
         <v>57740</v>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562543</v>
+        <v>562784</v>
       </c>
       <c r="R42" t="n">
-        <v>6954644</v>
+        <v>6954384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129986973</v>
+        <v>129981055</v>
       </c>
       <c r="B43" t="n">
-        <v>57740</v>
+        <v>91605</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5199,39 +5199,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562784</v>
+        <v>562686</v>
       </c>
       <c r="R43" t="n">
-        <v>6954384</v>
+        <v>6954603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5264,11 +5259,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129981055</v>
+        <v>129985572</v>
       </c>
       <c r="B44" t="n">
-        <v>91605</v>
+        <v>91625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5306,23 +5296,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5330,10 +5316,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562686</v>
+        <v>562648</v>
       </c>
       <c r="R44" t="n">
-        <v>6954603</v>
+        <v>6954498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5392,10 +5378,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129985572</v>
+        <v>129987434</v>
       </c>
       <c r="B45" t="n">
-        <v>91625</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5403,30 +5389,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562648</v>
+        <v>562873</v>
       </c>
       <c r="R45" t="n">
-        <v>6954498</v>
+        <v>6954448</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5485,10 +5484,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129987434</v>
+        <v>130015552</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5496,43 +5495,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, Lill-Tivsjön by, Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562873</v>
+        <v>562574</v>
       </c>
       <c r="R46" t="n">
-        <v>6954448</v>
+        <v>6954439</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5567,6 +5565,11 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran. Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5588,6 +5591,113 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129984997</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tivsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>562593</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6954431</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129986973</v>
+        <v>129981055</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>91605</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,39 +5092,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562784</v>
+        <v>562686</v>
       </c>
       <c r="R42" t="n">
-        <v>6954384</v>
+        <v>6954603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5157,11 +5152,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,10 +5178,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129981055</v>
+        <v>129986973</v>
       </c>
       <c r="B43" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5199,34 +5189,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562686</v>
+        <v>562784</v>
       </c>
       <c r="R43" t="n">
-        <v>6954603</v>
+        <v>6954384</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5259,6 +5254,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>129981126</v>
       </c>
       <c r="B24" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>129981204</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129981132</v>
+        <v>129987449</v>
       </c>
       <c r="B28" t="n">
-        <v>91903</v>
+        <v>91606</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562696</v>
+        <v>562883</v>
       </c>
       <c r="R28" t="n">
-        <v>6954608</v>
+        <v>6954461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129987449</v>
+        <v>129981136</v>
       </c>
       <c r="B29" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,34 +3755,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562883</v>
+        <v>562682</v>
       </c>
       <c r="R29" t="n">
-        <v>6954461</v>
+        <v>6954614</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,6 +3820,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,7 +3851,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129981136</v>
+        <v>129987474</v>
       </c>
       <c r="B30" t="n">
         <v>57740</v>
@@ -3881,10 +3891,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562682</v>
+        <v>562901</v>
       </c>
       <c r="R30" t="n">
-        <v>6954614</v>
+        <v>6954477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,7 +3958,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129987474</v>
+        <v>129984723</v>
       </c>
       <c r="B31" t="n">
         <v>57740</v>
@@ -3988,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562901</v>
+        <v>562591</v>
       </c>
       <c r="R31" t="n">
-        <v>6954477</v>
+        <v>6954478</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4055,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129984723</v>
+        <v>129981132</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>91904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,39 +4076,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562591</v>
+        <v>562696</v>
       </c>
       <c r="R32" t="n">
-        <v>6954478</v>
+        <v>6954608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4131,11 +4136,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,7 +4165,7 @@
         <v>129985202</v>
       </c>
       <c r="B33" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>129981053</v>
       </c>
       <c r="B34" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129982693</v>
+        <v>129986785</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,34 +4363,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562458</v>
+        <v>562725</v>
       </c>
       <c r="R35" t="n">
-        <v>6954577</v>
+        <v>6954475</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4423,6 +4428,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4449,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129986785</v>
+        <v>129982693</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,39 +4470,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562725</v>
+        <v>562458</v>
       </c>
       <c r="R36" t="n">
-        <v>6954475</v>
+        <v>6954577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4525,11 +4530,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4666,7 +4666,7 @@
         <v>129981038</v>
       </c>
       <c r="B38" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129981055</v>
+        <v>129986973</v>
       </c>
       <c r="B42" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,34 +5092,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562686</v>
+        <v>562784</v>
       </c>
       <c r="R42" t="n">
-        <v>6954603</v>
+        <v>6954384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5152,6 +5157,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5178,10 +5188,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129986973</v>
+        <v>129981055</v>
       </c>
       <c r="B43" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5189,39 +5199,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562784</v>
+        <v>562686</v>
       </c>
       <c r="R43" t="n">
-        <v>6954384</v>
+        <v>6954603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,11 +5259,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,7 +5288,7 @@
         <v>129985572</v>
       </c>
       <c r="B44" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>129981126</v>
       </c>
       <c r="B24" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>129981204</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129987449</v>
+        <v>129981132</v>
       </c>
       <c r="B28" t="n">
-        <v>91606</v>
+        <v>91921</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562883</v>
+        <v>562696</v>
       </c>
       <c r="R28" t="n">
-        <v>6954461</v>
+        <v>6954608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129981136</v>
+        <v>129987449</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,39 +3755,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562682</v>
+        <v>562883</v>
       </c>
       <c r="R29" t="n">
-        <v>6954614</v>
+        <v>6954461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3820,11 +3815,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3851,7 +3841,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129987474</v>
+        <v>129981136</v>
       </c>
       <c r="B30" t="n">
         <v>57740</v>
@@ -3891,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562901</v>
+        <v>562682</v>
       </c>
       <c r="R30" t="n">
-        <v>6954477</v>
+        <v>6954614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,7 +3948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129984723</v>
+        <v>129987474</v>
       </c>
       <c r="B31" t="n">
         <v>57740</v>
@@ -3998,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562591</v>
+        <v>562901</v>
       </c>
       <c r="R31" t="n">
-        <v>6954478</v>
+        <v>6954477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4065,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129981132</v>
+        <v>129984723</v>
       </c>
       <c r="B32" t="n">
-        <v>91904</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,34 +4066,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562696</v>
+        <v>562591</v>
       </c>
       <c r="R32" t="n">
-        <v>6954608</v>
+        <v>6954478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,6 +4131,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,7 +4165,7 @@
         <v>129985202</v>
       </c>
       <c r="B33" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>129981053</v>
       </c>
       <c r="B34" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129986785</v>
+        <v>129982693</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,39 +4363,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562725</v>
+        <v>562458</v>
       </c>
       <c r="R35" t="n">
-        <v>6954475</v>
+        <v>6954577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4428,11 +4423,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,10 +4449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129982693</v>
+        <v>129986785</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,34 +4460,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562458</v>
+        <v>562725</v>
       </c>
       <c r="R36" t="n">
-        <v>6954577</v>
+        <v>6954475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4530,6 +4525,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4666,7 +4666,7 @@
         <v>129981038</v>
       </c>
       <c r="B38" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129986973</v>
+        <v>129981055</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,39 +5092,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562784</v>
+        <v>562686</v>
       </c>
       <c r="R42" t="n">
-        <v>6954384</v>
+        <v>6954603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5157,11 +5152,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,10 +5178,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129981055</v>
+        <v>129986973</v>
       </c>
       <c r="B43" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5199,34 +5189,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562686</v>
+        <v>562784</v>
       </c>
       <c r="R43" t="n">
-        <v>6954603</v>
+        <v>6954384</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5259,6 +5254,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5285,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129985572</v>
+        <v>129987434</v>
       </c>
       <c r="B44" t="n">
-        <v>91626</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5296,30 +5296,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562648</v>
+        <v>562873</v>
       </c>
       <c r="R44" t="n">
-        <v>6954498</v>
+        <v>6954448</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,10 +5391,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129987434</v>
+        <v>129985572</v>
       </c>
       <c r="B45" t="n">
-        <v>57898</v>
+        <v>91643</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5389,43 +5402,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562873</v>
+        <v>562648</v>
       </c>
       <c r="R45" t="n">
-        <v>6954448</v>
+        <v>6954498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129981132</v>
+        <v>129987449</v>
       </c>
       <c r="B28" t="n">
-        <v>91937</v>
+        <v>91639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562696</v>
+        <v>562883</v>
       </c>
       <c r="R28" t="n">
-        <v>6954608</v>
+        <v>6954461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129987449</v>
+        <v>129981132</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>91937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,21 +3755,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562883</v>
+        <v>562696</v>
       </c>
       <c r="R29" t="n">
-        <v>6954461</v>
+        <v>6954608</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129987449</v>
+        <v>129981132</v>
       </c>
       <c r="B28" t="n">
-        <v>91639</v>
+        <v>91937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562883</v>
+        <v>562696</v>
       </c>
       <c r="R28" t="n">
-        <v>6954461</v>
+        <v>6954608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129981132</v>
+        <v>129987449</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>91639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,21 +3755,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562696</v>
+        <v>562883</v>
       </c>
       <c r="R29" t="n">
-        <v>6954608</v>
+        <v>6954461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3242,7 +3242,7 @@
         <v>129981126</v>
       </c>
       <c r="B24" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>129981132</v>
       </c>
       <c r="B28" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>129987449</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>129985202</v>
       </c>
       <c r="B33" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129982693</v>
+        <v>129981053</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>91939</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562458</v>
+        <v>562682</v>
       </c>
       <c r="R34" t="n">
-        <v>6954577</v>
+        <v>6954614</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129986785</v>
+        <v>129982693</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,39 +4363,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562725</v>
+        <v>562458</v>
       </c>
       <c r="R35" t="n">
-        <v>6954475</v>
+        <v>6954577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4428,11 +4423,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,10 +4449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129981053</v>
+        <v>129986785</v>
       </c>
       <c r="B36" t="n">
-        <v>91937</v>
+        <v>57741</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,34 +4460,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562682</v>
+        <v>562725</v>
       </c>
       <c r="R36" t="n">
-        <v>6954614</v>
+        <v>6954475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4530,6 +4525,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5084,7 +5084,7 @@
         <v>129981055</v>
       </c>
       <c r="B42" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129985572</v>
+        <v>129987434</v>
       </c>
       <c r="B44" t="n">
-        <v>91659</v>
+        <v>57900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5296,30 +5296,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562648</v>
+        <v>562873</v>
       </c>
       <c r="R44" t="n">
-        <v>6954498</v>
+        <v>6954448</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5378,10 +5391,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129987434</v>
+        <v>129985572</v>
       </c>
       <c r="B45" t="n">
-        <v>57900</v>
+        <v>91661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5389,43 +5402,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562873</v>
+        <v>562648</v>
       </c>
       <c r="R45" t="n">
-        <v>6954448</v>
+        <v>6954498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3135,7 +3135,7 @@
         <v>129985367</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129981126</v>
       </c>
       <c r="B24" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>129981204</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>129986595</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>129982476</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>129981132</v>
       </c>
       <c r="B28" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129987449</v>
+        <v>129981136</v>
       </c>
       <c r="B29" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,34 +3755,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562883</v>
+        <v>562682</v>
       </c>
       <c r="R29" t="n">
-        <v>6954461</v>
+        <v>6954614</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,6 +3820,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,10 +3851,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129981136</v>
+        <v>129987474</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3881,10 +3891,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562682</v>
+        <v>562901</v>
       </c>
       <c r="R30" t="n">
-        <v>6954614</v>
+        <v>6954477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129987474</v>
+        <v>129984723</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3988,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562901</v>
+        <v>562591</v>
       </c>
       <c r="R31" t="n">
-        <v>6954477</v>
+        <v>6954478</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4055,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129984723</v>
+        <v>129987449</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,39 +4076,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562591</v>
+        <v>562883</v>
       </c>
       <c r="R32" t="n">
-        <v>6954478</v>
+        <v>6954461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4131,11 +4136,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,7 +4165,7 @@
         <v>129985202</v>
       </c>
       <c r="B33" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129981053</v>
+        <v>129982693</v>
       </c>
       <c r="B34" t="n">
-        <v>91939</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562682</v>
+        <v>562458</v>
       </c>
       <c r="R34" t="n">
-        <v>6954614</v>
+        <v>6954577</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129982693</v>
+        <v>129986785</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,34 +4363,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562458</v>
+        <v>562725</v>
       </c>
       <c r="R35" t="n">
-        <v>6954577</v>
+        <v>6954475</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4423,6 +4428,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4449,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129986785</v>
+        <v>129981053</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>92026</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,39 +4470,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562725</v>
+        <v>562682</v>
       </c>
       <c r="R36" t="n">
-        <v>6954475</v>
+        <v>6954614</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4525,11 +4530,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4559,7 +4559,7 @@
         <v>129982927</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>129981038</v>
       </c>
       <c r="B38" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>129982656</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>129983882</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>129986495</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129981055</v>
+        <v>129986973</v>
       </c>
       <c r="B42" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,34 +5092,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562686</v>
+        <v>562784</v>
       </c>
       <c r="R42" t="n">
-        <v>6954603</v>
+        <v>6954384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5152,6 +5157,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5178,10 +5188,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129986973</v>
+        <v>129981055</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5189,39 +5199,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562784</v>
+        <v>562686</v>
       </c>
       <c r="R43" t="n">
-        <v>6954384</v>
+        <v>6954603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,11 +5259,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5288,7 +5288,7 @@
         <v>129987434</v>
       </c>
       <c r="B44" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>129985572</v>
       </c>
       <c r="B45" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>130015552</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>129984997</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129981132</v>
+        <v>129981136</v>
       </c>
       <c r="B28" t="n">
-        <v>92026</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,34 +3658,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562696</v>
+        <v>562682</v>
       </c>
       <c r="R28" t="n">
-        <v>6954608</v>
+        <v>6954614</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,6 +3723,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,7 +3754,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129981136</v>
+        <v>129984723</v>
       </c>
       <c r="B29" t="n">
         <v>57826</v>
@@ -3784,10 +3794,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562682</v>
+        <v>562591</v>
       </c>
       <c r="R29" t="n">
-        <v>6954614</v>
+        <v>6954478</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,10 +3861,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129987474</v>
+        <v>129987449</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,39 +3872,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562901</v>
+        <v>562883</v>
       </c>
       <c r="R30" t="n">
-        <v>6954477</v>
+        <v>6954461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3927,11 +3932,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129984723</v>
+        <v>129981132</v>
       </c>
       <c r="B31" t="n">
-        <v>57826</v>
+        <v>92026</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3969,39 +3969,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562591</v>
+        <v>562696</v>
       </c>
       <c r="R31" t="n">
-        <v>6954478</v>
+        <v>6954608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4034,11 +4029,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129987449</v>
+        <v>129987474</v>
       </c>
       <c r="B32" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,34 +4066,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562883</v>
+        <v>562901</v>
       </c>
       <c r="R32" t="n">
-        <v>6954461</v>
+        <v>6954477</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,6 +4131,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129986973</v>
+        <v>129981055</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,39 +5092,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562784</v>
+        <v>562686</v>
       </c>
       <c r="R42" t="n">
-        <v>6954384</v>
+        <v>6954603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5157,11 +5152,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5188,10 +5178,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129981055</v>
+        <v>129986973</v>
       </c>
       <c r="B43" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5199,34 +5189,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562686</v>
+        <v>562784</v>
       </c>
       <c r="R43" t="n">
-        <v>6954603</v>
+        <v>6954384</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5259,6 +5254,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5285,10 +5285,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129987434</v>
+        <v>129985572</v>
       </c>
       <c r="B44" t="n">
-        <v>57985</v>
+        <v>91748</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5296,43 +5296,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562873</v>
+        <v>562648</v>
       </c>
       <c r="R44" t="n">
-        <v>6954448</v>
+        <v>6954498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5391,10 +5378,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129985572</v>
+        <v>129987434</v>
       </c>
       <c r="B45" t="n">
-        <v>91748</v>
+        <v>57985</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5402,30 +5389,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562648</v>
+        <v>562873</v>
       </c>
       <c r="R45" t="n">
-        <v>6954498</v>
+        <v>6954448</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129981136</v>
+        <v>129981132</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>92026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,39 +3658,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562682</v>
+        <v>562696</v>
       </c>
       <c r="R28" t="n">
-        <v>6954614</v>
+        <v>6954608</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3723,11 +3718,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129984723</v>
+        <v>129987449</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3765,39 +3755,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562591</v>
+        <v>562883</v>
       </c>
       <c r="R29" t="n">
-        <v>6954478</v>
+        <v>6954461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,11 +3815,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3861,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129987449</v>
+        <v>129981136</v>
       </c>
       <c r="B30" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3872,34 +3852,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562883</v>
+        <v>562682</v>
       </c>
       <c r="R30" t="n">
-        <v>6954461</v>
+        <v>6954614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,6 +3917,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129981132</v>
+        <v>129987474</v>
       </c>
       <c r="B31" t="n">
-        <v>92026</v>
+        <v>57826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3969,34 +3959,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562696</v>
+        <v>562901</v>
       </c>
       <c r="R31" t="n">
-        <v>6954608</v>
+        <v>6954477</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4029,6 +4024,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129987474</v>
+        <v>129984723</v>
       </c>
       <c r="B32" t="n">
         <v>57826</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562901</v>
+        <v>562591</v>
       </c>
       <c r="R32" t="n">
-        <v>6954477</v>
+        <v>6954478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129982693</v>
+        <v>129981053</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562458</v>
+        <v>562682</v>
       </c>
       <c r="R34" t="n">
-        <v>6954577</v>
+        <v>6954614</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129986785</v>
+        <v>129982693</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,39 +4363,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562725</v>
+        <v>562458</v>
       </c>
       <c r="R35" t="n">
-        <v>6954475</v>
+        <v>6954577</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4428,11 +4423,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4459,10 +4449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129981053</v>
+        <v>129986785</v>
       </c>
       <c r="B36" t="n">
-        <v>92026</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,34 +4460,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562682</v>
+        <v>562725</v>
       </c>
       <c r="R36" t="n">
-        <v>6954614</v>
+        <v>6954475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4530,6 +4525,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129981132</v>
+        <v>129987449</v>
       </c>
       <c r="B28" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562696</v>
+        <v>562883</v>
       </c>
       <c r="R28" t="n">
-        <v>6954608</v>
+        <v>6954461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129987449</v>
+        <v>129981136</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3755,34 +3755,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562883</v>
+        <v>562682</v>
       </c>
       <c r="R29" t="n">
-        <v>6954461</v>
+        <v>6954614</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,6 +3820,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,7 +3851,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129981136</v>
+        <v>129987474</v>
       </c>
       <c r="B30" t="n">
         <v>57826</v>
@@ -3881,10 +3891,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562682</v>
+        <v>562901</v>
       </c>
       <c r="R30" t="n">
-        <v>6954614</v>
+        <v>6954477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,7 +3958,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129987474</v>
+        <v>129984723</v>
       </c>
       <c r="B31" t="n">
         <v>57826</v>
@@ -3988,10 +3998,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562901</v>
+        <v>562591</v>
       </c>
       <c r="R31" t="n">
-        <v>6954477</v>
+        <v>6954478</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4055,10 +4065,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129984723</v>
+        <v>129981132</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>92026</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,39 +4076,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562591</v>
+        <v>562696</v>
       </c>
       <c r="R32" t="n">
-        <v>6954478</v>
+        <v>6954608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4131,11 +4136,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129981053</v>
+        <v>129986785</v>
       </c>
       <c r="B34" t="n">
-        <v>92026</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,34 +4266,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562682</v>
+        <v>562725</v>
       </c>
       <c r="R34" t="n">
-        <v>6954614</v>
+        <v>6954475</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4326,6 +4331,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4352,10 +4362,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129982693</v>
+        <v>129981053</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,21 +4373,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4387,10 +4397,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562458</v>
+        <v>562682</v>
       </c>
       <c r="R35" t="n">
-        <v>6954577</v>
+        <v>6954614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4449,10 +4459,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129986785</v>
+        <v>129982693</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4460,39 +4470,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562725</v>
+        <v>562458</v>
       </c>
       <c r="R36" t="n">
-        <v>6954475</v>
+        <v>6954577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4525,11 +4530,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -675,53 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790172</v>
+        <v>111577180</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562666.0807293354</v>
+        <v>562883</v>
       </c>
       <c r="R2" t="n">
-        <v>6954597.719885167</v>
+        <v>6954442</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +767,65 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre blåbärstallskog med granunderväxt</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790165</v>
+        <v>111577273</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562506.1849548876</v>
+        <v>562825</v>
       </c>
       <c r="R3" t="n">
-        <v>6954620.840248522</v>
+        <v>6954323</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,78 +875,65 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>äldre mossig granskog i sydlut</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790169</v>
+        <v>111577994</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562705.2413112028</v>
+        <v>562890</v>
       </c>
       <c r="R4" t="n">
-        <v>6954447.488916199</v>
+        <v>6954487</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,40 +973,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>äldre blåbärstallskog med inslag av gran och lärk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96790166</v>
+        <v>129981053</v>
       </c>
       <c r="B5" t="n">
-        <v>86210</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,34 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562496.9241167592</v>
+        <v>562682</v>
       </c>
       <c r="R5" t="n">
-        <v>6954551.832277372</v>
+        <v>6954614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,75 +1070,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre mossig barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96790171</v>
+        <v>129981132</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562613.5919890646</v>
+        <v>562696</v>
       </c>
       <c r="R6" t="n">
-        <v>6954506.32153387</v>
+        <v>6954608</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,22 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,78 +1167,65 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre blåbärstallskog med inslag av gran och lärk</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96790167</v>
+        <v>111577080</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562878.6179939224</v>
+        <v>562937</v>
       </c>
       <c r="R7" t="n">
-        <v>6954320.460082462</v>
+        <v>6954467</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,22 +1249,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,78 +1275,65 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre mossig granskog i sydlut</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96790168</v>
+        <v>111578090</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tivsjöflon, SV om, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562830.2588961414</v>
+        <v>562890</v>
       </c>
       <c r="R8" t="n">
-        <v>6954374.149311617</v>
+        <v>6954487</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,22 +1357,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,82 +1383,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre mossig granskog i sydlut</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97082382</v>
+        <v>129981055</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tivsjöflon /SV/, skog SV om vägkors, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562595.7477789607</v>
+        <v>562686</v>
       </c>
       <c r="R9" t="n">
-        <v>6954574.816079412</v>
+        <v>6954603</v>
       </c>
       <c r="S9" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,34 +1462,14 @@
           <t>Hällesjö</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Z-Brä-1789</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterad på tre platser med namn Tivsjöflon, SV om. Koordinat O1521452 N6956135 (±10m), O1521506 N6956226 (±10m) och O1521346 N6956251 (±10m) RT90 2.5 gon. Summerat till Floraväkteriet.</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,43 +1478,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>äldre blåbärstallskog med inslag av gran och lärk/ do  med granunderväxt/ äldre mossig granskog i sydlut</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111577591</v>
+        <v>129987449</v>
       </c>
       <c r="B10" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,43 +1507,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562822.1033927511</v>
+        <v>562883</v>
       </c>
       <c r="R10" t="n">
-        <v>6954368.028004575</v>
+        <v>6954461</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,22 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,49 +1581,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111577964</v>
+        <v>111577193</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1817,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562836.2055113926</v>
+        <v>562885</v>
       </c>
       <c r="R11" t="n">
-        <v>6954423.824987715</v>
+        <v>6954428</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1852,7 +1664,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1862,7 +1674,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,54 +1701,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111575408</v>
+        <v>129981126</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562539.034657649</v>
+        <v>562686</v>
       </c>
       <c r="R12" t="n">
-        <v>6954609.073577877</v>
+        <v>6954603</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1960,22 +1766,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:21</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,66 +1786,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111577804</v>
+        <v>96790166</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562814.775380839</v>
+        <v>562497</v>
       </c>
       <c r="R13" t="n">
-        <v>6954390.834027934</v>
+        <v>6954552</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,22 +1863,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,31 +1879,35 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre mossig barrblandskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111577193</v>
+        <v>129981204</v>
       </c>
       <c r="B14" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,38 +1915,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562885.3077477051</v>
+        <v>562645</v>
       </c>
       <c r="R14" t="n">
-        <v>6954427.514711756</v>
+        <v>6954638</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2186,22 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,66 +1989,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111578062</v>
+        <v>129982693</v>
       </c>
       <c r="B15" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562890.6102569005</v>
+        <v>562458</v>
       </c>
       <c r="R15" t="n">
-        <v>6954486.814324431</v>
+        <v>6954577</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2299,22 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,27 +2086,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111577080</v>
+        <v>129981038</v>
       </c>
       <c r="B16" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,38 +2109,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562937.8525077751</v>
+        <v>562680</v>
       </c>
       <c r="R16" t="n">
-        <v>6954467.524316943</v>
+        <v>6954592</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2412,22 +2163,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,27 +2183,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111577180</v>
+        <v>129981136</v>
       </c>
       <c r="B17" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,38 +2206,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562883.198926247</v>
+        <v>562682</v>
       </c>
       <c r="R17" t="n">
-        <v>6954441.700568204</v>
+        <v>6954614</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2525,22 +2265,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2555,27 +2290,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111577273</v>
+        <v>129982476</v>
       </c>
       <c r="B18" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,38 +2313,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562824.7977144517</v>
+        <v>562483</v>
       </c>
       <c r="R18" t="n">
-        <v>6954323.105396069</v>
+        <v>6954658</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2638,22 +2372,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:24</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,66 +2397,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111577347</v>
+        <v>129982656</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562796.503171768</v>
+        <v>562447</v>
       </c>
       <c r="R19" t="n">
-        <v>6954336.792844097</v>
+        <v>6954609</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2751,22 +2479,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,66 +2504,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111577611</v>
+        <v>129982927</v>
       </c>
       <c r="B20" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562810.9079359611</v>
+        <v>562571</v>
       </c>
       <c r="R20" t="n">
-        <v>6954400.856378952</v>
+        <v>6954552</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2864,22 +2586,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,27 +2611,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111578090</v>
+        <v>129983882</v>
       </c>
       <c r="B21" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,38 +2634,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562890.6102569005</v>
+        <v>562540</v>
       </c>
       <c r="R21" t="n">
-        <v>6954486.814324431</v>
+        <v>6954488</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2977,22 +2693,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3007,66 +2718,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111577838</v>
+        <v>129984723</v>
       </c>
       <c r="B22" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562801.9298062191</v>
+        <v>562591</v>
       </c>
       <c r="R22" t="n">
-        <v>6954389.67147268</v>
+        <v>6954478</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,22 +2800,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18:14</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:14</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,22 +2825,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129985367</v>
+        <v>129984997</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3172,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562633</v>
+        <v>562593</v>
       </c>
       <c r="R23" t="n">
-        <v>6954441</v>
+        <v>6954431</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3239,45 +2944,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129981126</v>
+        <v>129985367</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562686</v>
+        <v>562633</v>
       </c>
       <c r="R24" t="n">
-        <v>6954603</v>
+        <v>6954441</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,6 +3020,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,10 +3051,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129981204</v>
+        <v>129986495</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,34 +3062,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562645</v>
+        <v>562543</v>
       </c>
       <c r="R25" t="n">
-        <v>6954638</v>
+        <v>6954644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3407,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,7 +3161,7 @@
         <v>129986595</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3540,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129982476</v>
+        <v>129986785</v>
       </c>
       <c r="B27" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3580,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562483</v>
+        <v>562725</v>
       </c>
       <c r="R27" t="n">
-        <v>6954658</v>
+        <v>6954475</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3647,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129987449</v>
+        <v>129986973</v>
       </c>
       <c r="B28" t="n">
-        <v>91728</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3658,34 +3383,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562883</v>
+        <v>562784</v>
       </c>
       <c r="R28" t="n">
-        <v>6954461</v>
+        <v>6954384</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,6 +3448,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129981136</v>
+        <v>129987474</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562682</v>
+        <v>562901</v>
       </c>
       <c r="R29" t="n">
-        <v>6954614</v>
+        <v>6954477</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3851,10 +3586,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129987474</v>
+        <v>130015552</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3615,24 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, Lill-Tivsjön by, Hällesjö, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562901</v>
+        <v>562574</v>
       </c>
       <c r="R30" t="n">
-        <v>6954477</v>
+        <v>6954439</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,7 +3669,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran. Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3696,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129984723</v>
+        <v>111577591</v>
       </c>
       <c r="B31" t="n">
-        <v>57826</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3969,27 +3707,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3998,13 +3737,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562591</v>
+        <v>562823</v>
       </c>
       <c r="R31" t="n">
-        <v>6954478</v>
+        <v>6954368</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4028,17 +3767,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,22 +3787,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129981132</v>
+        <v>111578127</v>
       </c>
       <c r="B32" t="n">
-        <v>92026</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4076,37 +3810,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562696</v>
+        <v>562938</v>
       </c>
       <c r="R32" t="n">
-        <v>6954608</v>
+        <v>6954541</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4130,12 +3870,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,22 +3900,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129985202</v>
+        <v>129987434</v>
       </c>
       <c r="B33" t="n">
-        <v>91748</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4173,30 +3923,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562577</v>
+        <v>562873</v>
       </c>
       <c r="R33" t="n">
-        <v>6954432</v>
+        <v>6954448</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4255,45 +4018,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129981053</v>
+        <v>96790165</v>
       </c>
       <c r="B34" t="n">
-        <v>92026</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562682</v>
+        <v>562506</v>
       </c>
       <c r="R34" t="n">
-        <v>6954614</v>
+        <v>6954621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4320,12 +4083,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4336,66 +4099,70 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre mossig granskog i sydlut</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129986785</v>
+        <v>96790167</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562725</v>
+        <v>562879</v>
       </c>
       <c r="R35" t="n">
-        <v>6954475</v>
+        <v>6954321</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4422,17 +4189,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4443,61 +4205,70 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>äldre mossig granskog i sydlut</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129982693</v>
+        <v>96790168</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562458</v>
+        <v>562830</v>
       </c>
       <c r="R36" t="n">
-        <v>6954577</v>
+        <v>6954374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4524,12 +4295,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4540,66 +4311,70 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>äldre mossig granskog i sydlut</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129982927</v>
+        <v>96790169</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562571</v>
+        <v>562705</v>
       </c>
       <c r="R37" t="n">
-        <v>6954552</v>
+        <v>6954447</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,17 +4401,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4647,61 +4417,70 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog med inslag av gran och lärk</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129981038</v>
+        <v>96790171</v>
       </c>
       <c r="B38" t="n">
-        <v>80285</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562680</v>
+        <v>562613</v>
       </c>
       <c r="R38" t="n">
-        <v>6954592</v>
+        <v>6954506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,12 +4507,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4744,66 +4523,70 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog med inslag av gran och lärk</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129982656</v>
+        <v>96790172</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562447</v>
+        <v>562666</v>
       </c>
       <c r="R39" t="n">
-        <v>6954609</v>
+        <v>6954598</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4830,17 +4613,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4851,69 +4629,77 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog med granunderväxt</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129983882</v>
+        <v>97082382</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Jmt</t>
+          <t>Tivsjöflon /SV/, skog SV om vägkors, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562540</v>
+        <v>562596</v>
       </c>
       <c r="R40" t="n">
-        <v>6954488</v>
+        <v>6954575</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4935,19 +4721,24 @@
           <t>Hällesjö</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Z-Brä-1789</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Noterad på tre platser med namn Tivsjöflon, SV om. Koordinat O1521452 N6956135 (±10m), O1521506 N6956226 (±10m) och O1521346 N6956251 (±10m) RT90 2.5 gon. Summerat till Floraväkteriet.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4956,71 +4747,77 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>äldre blåbärstallskog med inslag av gran och lärk/ do  med granunderväxt/ äldre mossig granskog i sydlut</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129986495</v>
+        <v>111575408</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562543</v>
+        <v>562539</v>
       </c>
       <c r="R41" t="n">
-        <v>6954644</v>
+        <v>6954609</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5044,17 +4841,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5069,65 +4871,61 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129986973</v>
+        <v>111577347</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562784</v>
+        <v>562797</v>
       </c>
       <c r="R42" t="n">
-        <v>6954384</v>
+        <v>6954336</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5151,17 +4949,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5176,60 +4969,61 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129981055</v>
+        <v>111577611</v>
       </c>
       <c r="B43" t="n">
-        <v>91728</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562686</v>
+        <v>562811</v>
       </c>
       <c r="R43" t="n">
-        <v>6954603</v>
+        <v>6954401</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5253,12 +5047,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5273,56 +5067,61 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129985572</v>
+        <v>111577743</v>
       </c>
       <c r="B44" t="n">
-        <v>91748</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562648</v>
+        <v>562803</v>
       </c>
       <c r="R44" t="n">
-        <v>6954498</v>
+        <v>6954389</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5346,12 +5145,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5366,69 +5175,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129987434</v>
+        <v>111577804</v>
       </c>
       <c r="B45" t="n">
-        <v>57985</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562873</v>
+        <v>562815</v>
       </c>
       <c r="R45" t="n">
-        <v>6954448</v>
+        <v>6954391</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5452,12 +5253,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5472,68 +5273,61 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130015552</v>
+        <v>111577838</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tivsjöflon, Lill-Tivsjön by, Hällesjö, Jmt</t>
+          <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562574</v>
+        <v>562802</v>
       </c>
       <c r="R46" t="n">
-        <v>6954439</v>
+        <v>6954390</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5557,17 +5351,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sannolikt påbörjat bobygge av tretåig hackspett i grantickerötad gran. Bohålskammaren är ej färdig. Drygt 2 meter ovan mark. Omkring 4,5 cm i bohålsdiameter</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5582,65 +5381,61 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129984997</v>
+        <v>111577919</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tivsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562593</v>
+        <v>562836</v>
       </c>
       <c r="R47" t="n">
-        <v>6954431</v>
+        <v>6954424</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5664,17 +5459,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5689,12 +5479,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 49540-2022 artfynd.xlsx
+++ b/artfynd/A 49540-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577180</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577994</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981053</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981132</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577080</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578090</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981055</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987449</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577193</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981126</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790166</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981204</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129982693</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981038</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129981136</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129982476</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2513,6 +2603,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129982656</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129982927</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2727,6 +2827,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129983882</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2834,6 +2939,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129984723</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2941,6 +3051,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129984997</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3048,6 +3163,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129985367</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3155,6 +3275,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986495</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986595</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3369,6 +3499,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986785</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3476,6 +3611,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129986973</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3583,6 +3723,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987474</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3693,6 +3838,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130015552</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3796,6 +3946,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577591</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3909,6 +4064,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578127</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4015,6 +4175,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987434</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4121,6 +4286,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790165</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4227,6 +4397,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790167</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4333,6 +4508,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790168</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4439,6 +4619,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790169</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4545,6 +4730,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790171</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4649,6 +4839,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790172</t>
         </is>
       </c>
     </row>
@@ -4772,6 +4967,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97082382</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4880,6 +5080,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111575408</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4978,6 +5183,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577347</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5076,6 +5286,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577611</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5184,6 +5399,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577743</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5282,6 +5502,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577804</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5390,6 +5615,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577838</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5488,8 +5718,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111577919</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>